--- a/Configs/GameConfig/Datas/界面UI.xlsx
+++ b/Configs/GameConfig/Datas/界面UI.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Godot-Project\StartFromZero\Configs\GameConfig\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790"/>
+    <workbookView windowHeight="17500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,10 +136,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -642,19 +647,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
